--- a/reports/daily_visits.xlsx
+++ b/reports/daily_visits.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -427,16 +427,17 @@
     <col width="37" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,50 +468,55 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Mojo Godi</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Moses Thulare Moshwane</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Nolwazi Natasha Adams</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Ntombizodwa Zodwa Dubazana</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Onalenna Maisa</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Perseverance G Merafe</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Phamela Z Mayisela</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Refilwe Prudence Mgidi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Saziso Veli Nhlozi</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Thabo Caiphas Mosa</t>
         </is>
@@ -538,11 +544,11 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -562,6 +568,9 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -584,33 +593,36 @@
         <v>12</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>3</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>15</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>17</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>4</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>11</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>15</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -639,27 +651,30 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>9</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>21</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>20</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>19</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>14</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>20</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -670,17 +685,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" t="n">
         <v>15</v>
       </c>
-      <c r="E5" t="n">
-        <v>11</v>
-      </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
@@ -688,28 +703,83 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>21</v>
+      </c>
+      <c r="L5" t="n">
+        <v>21</v>
+      </c>
+      <c r="M5" t="n">
+        <v>21</v>
+      </c>
+      <c r="N5" t="n">
         <v>15</v>
       </c>
-      <c r="K5" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>11</v>
-      </c>
-      <c r="N5" t="n">
-        <v>16</v>
-      </c>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>25</v>
+      </c>
+      <c r="P5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>09-Oct-25</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
